--- a/data/trans_dic/P44-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,87</t>
+          <t>3,28; 8,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,4</t>
+          <t>7,61; 15,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,01; 35,51</t>
+          <t>26,53; 35,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,48</t>
+          <t>3,28; 8,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 12,45</t>
+          <t>5,56; 11,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,6; 31,05</t>
+          <t>24,59; 31,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,79</t>
+          <t>3,91; 7,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 12,4</t>
+          <t>7,32; 12,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,88; 32,09</t>
+          <t>26,75; 32,26</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,46</t>
+          <t>5,54; 12,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 13,18</t>
+          <t>7,13; 13,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,48; 84,62</t>
+          <t>34,48; 84,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,35</t>
+          <t>6,67; 12,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,56</t>
+          <t>5,11; 10,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,56; 32,95</t>
+          <t>26,35; 32,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,56</t>
+          <t>7,17; 11,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,79</t>
+          <t>6,66; 10,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,74; 72,03</t>
+          <t>31,72; 73,04</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 17,4</t>
+          <t>7,49; 17,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 16,95</t>
+          <t>8,25; 15,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,11; 38,43</t>
+          <t>28,7; 38,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,91</t>
+          <t>5,55; 13,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,37</t>
+          <t>4,04; 10,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 25,37</t>
+          <t>4,42; 25,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,62</t>
+          <t>7,56; 13,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 11,96</t>
+          <t>6,66; 11,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 29,89</t>
+          <t>10,5; 30,35</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 15,96</t>
+          <t>8,46; 15,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 18,34</t>
+          <t>11,0; 17,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,34; 47,35</t>
+          <t>39,09; 47,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,73</t>
+          <t>4,05; 9,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,36</t>
+          <t>5,06; 9,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,71; 37,85</t>
+          <t>31,32; 38,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,91</t>
+          <t>6,7; 11,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,61</t>
+          <t>8,49; 12,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,14; 41,13</t>
+          <t>36,02; 41,11</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,58</t>
+          <t>7,7; 11,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 13,72</t>
+          <t>10,11; 13,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,86; 66,53</t>
+          <t>35,77; 65,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,95</t>
+          <t>6,23; 9,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,89</t>
+          <t>6,26; 9,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 30,46</t>
+          <t>16,78; 30,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 9,56</t>
+          <t>7,39; 9,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,37; 10,58</t>
+          <t>8,5; 10,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,41; 49,26</t>
+          <t>29,14; 49,69</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8357; 23692</t>
+          <t>8772; 23116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22072; 44902</t>
+          <t>22186; 44726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78048; 106541</t>
+          <t>79583; 107086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9347; 25406</t>
+          <t>9841; 25606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18825; 40210</t>
+          <t>17960; 38623</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86316; 108959</t>
+          <t>86276; 110016</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21327; 44169</t>
+          <t>22163; 44539</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46505; 76191</t>
+          <t>44994; 76499</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>174996; 208850</t>
+          <t>174145; 209958</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17964; 41339</t>
+          <t>18357; 41309</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30141; 53475</t>
+          <t>28950; 53864</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>221847; 544400</t>
+          <t>221810; 543660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26212; 48856</t>
+          <t>26395; 50877</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23950; 49439</t>
+          <t>23916; 48695</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>113807; 141200</t>
+          <t>112929; 140062</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51454; 84062</t>
+          <t>52167; 84125</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58643; 94338</t>
+          <t>58246; 93293</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>340227; 772076</t>
+          <t>339959; 782929</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18932; 42641</t>
+          <t>18363; 42519</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23429; 48117</t>
+          <t>23436; 44697</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93796; 123839</t>
+          <t>92479; 124907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18195; 39121</t>
+          <t>16822; 39435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12215; 30785</t>
+          <t>11988; 30062</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24256; 126924</t>
+          <t>22127; 127181</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43053; 74635</t>
+          <t>41415; 73438</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39636; 69439</t>
+          <t>38698; 67609</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73150; 245847</t>
+          <t>86401; 249623</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28486; 55894</t>
+          <t>29620; 55655</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47839; 76709</t>
+          <t>45989; 74280</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174855; 210423</t>
+          <t>173710; 211230</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18950; 40966</t>
+          <t>19015; 42268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25861; 52606</t>
+          <t>25712; 48810</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167528; 199961</t>
+          <t>165467; 201013</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54855; 89409</t>
+          <t>54876; 90626</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79309; 116727</t>
+          <t>78610; 119036</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>351539; 400100</t>
+          <t>350395; 399884</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92764; 138282</t>
+          <t>91941; 138120</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>141704; 191956</t>
+          <t>141503; 191432</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>613221; 1137669</t>
+          <t>611744; 1112299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89516; 131398</t>
+          <t>91432; 133802</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98308; 141896</t>
+          <t>99931; 145022</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>315898; 550702</t>
+          <t>303346; 548100</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>194216; 254540</t>
+          <t>196684; 256243</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>250835; 316911</t>
+          <t>254479; 319383</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1034627; 1733043</t>
+          <t>1025251; 1748115</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,66</t>
+          <t>3,43; 8,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 15,34</t>
+          <t>7,66; 15,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,53; 35,69</t>
+          <t>26,58; 35,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,54</t>
+          <t>3,05; 8,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 11,96</t>
+          <t>5,51; 12,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,59; 31,35</t>
+          <t>25,1; 31,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,86</t>
+          <t>3,86; 7,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 12,45</t>
+          <t>7,35; 12,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,75; 32,26</t>
+          <t>26,77; 32,24</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,46</t>
+          <t>5,59; 12,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 13,27</t>
+          <t>7,32; 13,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,48; 84,51</t>
+          <t>31,54; 40,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,86</t>
+          <t>6,89; 12,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,4</t>
+          <t>5,17; 10,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,35; 32,68</t>
+          <t>26,58; 32,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,57</t>
+          <t>6,87; 11,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,67</t>
+          <t>6,91; 10,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 73,04</t>
+          <t>30,09; 35,31</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 17,35</t>
+          <t>7,52; 17,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 15,74</t>
+          <t>8,08; 15,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 38,76</t>
+          <t>28,39; 37,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 13,01</t>
+          <t>6,25; 13,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,13</t>
+          <t>4,18; 10,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 25,42</t>
+          <t>21,72; 29,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,4</t>
+          <t>7,65; 13,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,64</t>
+          <t>6,99; 11,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 30,35</t>
+          <t>26,03; 32,41</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 15,89</t>
+          <t>8,22; 16,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,76</t>
+          <t>11,3; 18,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,09; 47,53</t>
+          <t>39,0; 47,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,01</t>
+          <t>4,15; 8,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,61</t>
+          <t>5,24; 10,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,32; 38,05</t>
+          <t>31,76; 38,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,06</t>
+          <t>6,84; 11,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,86</t>
+          <t>8,57; 12,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,02; 41,11</t>
+          <t>36,22; 41,39</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,57</t>
+          <t>7,78; 11,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,68</t>
+          <t>10,03; 13,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,77; 65,05</t>
+          <t>33,94; 38,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,12</t>
+          <t>6,15; 8,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,09</t>
+          <t>6,16; 8,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 30,32</t>
+          <t>28,61; 31,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,63</t>
+          <t>7,31; 9,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,66</t>
+          <t>8,46; 10,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,14; 49,69</t>
+          <t>31,62; 34,44</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97661</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>208654</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8772; 23116</t>
+          <t>9167; 23810</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22186; 44726</t>
+          <t>22325; 43958</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79583; 107086</t>
+          <t>87701; 117677</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9841; 25606</t>
+          <t>9149; 25666</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17960; 38623</t>
+          <t>17787; 40256</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86276; 110016</t>
+          <t>94728; 119115</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22163; 44539</t>
+          <t>21891; 43922</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44994; 76499</t>
+          <t>45153; 76495</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>174145; 209958</t>
+          <t>189357; 228068</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386980</t>
+          <t>153970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>514163</t>
+          <t>294303</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18357; 41309</t>
+          <t>18522; 40952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28950; 53864</t>
+          <t>29726; 55248</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>221810; 543660</t>
+          <t>135971; 173593</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26395; 50877</t>
+          <t>27248; 50562</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23916; 48695</t>
+          <t>24220; 49619</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>112929; 140062</t>
+          <t>125563; 155389</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52167; 84125</t>
+          <t>49949; 83481</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58246; 93293</t>
+          <t>60363; 95520</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>339959; 782929</t>
+          <t>271883; 319010</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107725</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72306</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180030</t>
+          <t>204190</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18363; 42519</t>
+          <t>18420; 42791</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23436; 44697</t>
+          <t>22926; 44846</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92479; 124907</t>
+          <t>103775; 138259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16822; 39435</t>
+          <t>18932; 40415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11988; 30062</t>
+          <t>12415; 30771</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22127; 127181</t>
+          <t>73277; 98535</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41415; 73438</t>
+          <t>41905; 75503</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38698; 67609</t>
+          <t>40613; 69327</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86401; 249623</t>
+          <t>183006; 227865</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192807</t>
+          <t>200195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>182272</t>
+          <t>198125</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>375079</t>
+          <t>398320</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29620; 55655</t>
+          <t>28800; 56165</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45989; 74280</t>
+          <t>47249; 76476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>173710; 211230</t>
+          <t>182278; 219822</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19015; 42268</t>
+          <t>19450; 40777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25712; 48810</t>
+          <t>26626; 52405</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>165467; 201013</t>
+          <t>179198; 216492</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54876; 90626</t>
+          <t>56005; 90233</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78610; 119036</t>
+          <t>79307; 117918</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>350395; 399884</t>
+          <t>373614; 427031</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>780497</t>
+          <t>575464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1259920</t>
+          <t>1105467</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>91941; 138120</t>
+          <t>92930; 136953</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>141503; 191432</t>
+          <t>140424; 189496</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>611744; 1112299</t>
+          <t>540928; 611536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91432; 133802</t>
+          <t>90234; 131805</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99931; 145022</t>
+          <t>98230; 143470</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>303346; 548100</t>
+          <t>501033; 558655</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>196684; 256243</t>
+          <t>194689; 257344</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>254479; 319383</t>
+          <t>253370; 322040</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1025251; 1748115</t>
+          <t>1057958; 1152250</t>
         </is>
       </c>
     </row>
